--- a/excel-example/Old/Перевод позиций FOR MAPPING .xlsx
+++ b/excel-example/Old/Перевод позиций FOR MAPPING .xlsx
@@ -169,9 +169,6 @@
     <t>Anchor wedge MAN</t>
   </si>
   <si>
-    <t>screws universal yellow</t>
-  </si>
-  <si>
     <t xml:space="preserve">screws сountersunk structural self-tapping </t>
   </si>
   <si>
@@ -202,9 +199,6 @@
     <t>DIN766 chain SHORT link</t>
   </si>
   <si>
-    <t>DIN 3055 braided rope 6x7</t>
-  </si>
-  <si>
     <t xml:space="preserve">screws reinforced </t>
   </si>
   <si>
@@ -214,12 +208,6 @@
     <t>screws with disc head</t>
   </si>
   <si>
-    <t>screws for metall DRILL PHOSPHAT PMS</t>
-  </si>
-  <si>
-    <t>screws for metall SHARP PHOSPHAT PM</t>
-  </si>
-  <si>
     <t>screws Fluegel zinc</t>
   </si>
   <si>
@@ -242,6 +230,18 @@
   </si>
   <si>
     <t xml:space="preserve">Саморезы гипс/дерево(3.5) </t>
+  </si>
+  <si>
+    <t>DIN 3055 braided rope</t>
+  </si>
+  <si>
+    <t>screws for metal DRILL PHOSPHAT PMS</t>
+  </si>
+  <si>
+    <t>screws for metal SHARP PHOSPHAT PM</t>
+  </si>
+  <si>
+    <t>screws UNIVERSAL yellow part thread</t>
   </si>
 </sst>
 </file>
@@ -642,7 +642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr defaultRowHeight="40.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="69.85546875" style="1" customWidth="1"/>
@@ -667,7 +667,7 @@
         <v>49</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>24</v>
@@ -681,7 +681,7 @@
         <v>50</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>39</v>
@@ -692,10 +692,10 @@
     </row>
     <row r="4" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>22</v>
@@ -706,13 +706,13 @@
     </row>
     <row r="5" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>33</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="6" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>20</v>
@@ -734,10 +734,10 @@
     </row>
     <row r="7" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>21</v>
@@ -751,7 +751,7 @@
         <v>48</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>4</v>
@@ -762,10 +762,10 @@
     </row>
     <row r="9" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>46</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="10" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>15</v>
@@ -791,10 +791,10 @@
     </row>
     <row r="11" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>42</v>
@@ -805,10 +805,10 @@
     </row>
     <row r="12" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>41</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="13" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>44</v>
@@ -833,10 +833,10 @@
     </row>
     <row r="14" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>45</v>
@@ -847,52 +847,52 @@
     </row>
     <row r="15" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>7</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="19" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>23</v>
@@ -917,10 +917,10 @@
     </row>
     <row r="20" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>13</v>
@@ -931,10 +931,10 @@
     </row>
     <row r="21" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>25</v>
@@ -945,10 +945,10 @@
     </row>
     <row r="22" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>19</v>
@@ -959,10 +959,10 @@
     </row>
     <row r="23" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>5</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="24" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>17</v>
@@ -987,10 +987,10 @@
     </row>
     <row r="25" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>40</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="26" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>3</v>
@@ -1014,10 +1014,175 @@
         <v>2</v>
       </c>
     </row>
+    <row r="33" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33"/>
+      <c r="B33"/>
+      <c r="C33"/>
+      <c r="E33"/>
+    </row>
+    <row r="34" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34"/>
+      <c r="B34"/>
+      <c r="C34"/>
+      <c r="E34"/>
+    </row>
+    <row r="35" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35"/>
+      <c r="B35"/>
+      <c r="C35"/>
+      <c r="E35"/>
+    </row>
+    <row r="36" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36"/>
+      <c r="B36"/>
+      <c r="C36"/>
+      <c r="E36"/>
+    </row>
+    <row r="37" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37"/>
+      <c r="B37"/>
+      <c r="C37"/>
+      <c r="E37"/>
+    </row>
+    <row r="38" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38"/>
+      <c r="B38"/>
+      <c r="C38"/>
+      <c r="E38"/>
+    </row>
+    <row r="39" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39"/>
+      <c r="B39"/>
+      <c r="C39"/>
+      <c r="E39"/>
+    </row>
+    <row r="40" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40"/>
+      <c r="B40"/>
+      <c r="C40"/>
+      <c r="E40"/>
+    </row>
+    <row r="41" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41"/>
+      <c r="B41"/>
+      <c r="C41"/>
+      <c r="E41"/>
+    </row>
+    <row r="42" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42"/>
+      <c r="B42"/>
+      <c r="C42"/>
+      <c r="E42"/>
+    </row>
+    <row r="43" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43"/>
+      <c r="B43"/>
+      <c r="C43"/>
+      <c r="E43"/>
+    </row>
+    <row r="44" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44"/>
+      <c r="B44"/>
+      <c r="C44"/>
+      <c r="E44"/>
+    </row>
+    <row r="45" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45"/>
+      <c r="B45"/>
+      <c r="C45"/>
+      <c r="E45"/>
+    </row>
+    <row r="46" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46"/>
+      <c r="B46"/>
+      <c r="C46"/>
+      <c r="E46"/>
+    </row>
+    <row r="47" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47"/>
+      <c r="B47"/>
+      <c r="C47"/>
+      <c r="E47"/>
+    </row>
+    <row r="48" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48"/>
+      <c r="B48"/>
+      <c r="C48"/>
+      <c r="E48"/>
+    </row>
+    <row r="49" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49"/>
+      <c r="B49"/>
+      <c r="C49"/>
+      <c r="E49"/>
+    </row>
+    <row r="50" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50"/>
+      <c r="B50"/>
+      <c r="C50"/>
+      <c r="E50"/>
+    </row>
+    <row r="51" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51"/>
+      <c r="B51"/>
+      <c r="C51"/>
+      <c r="E51"/>
+    </row>
+    <row r="52" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52"/>
+      <c r="B52"/>
+      <c r="C52"/>
+      <c r="E52"/>
+    </row>
+    <row r="53" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53"/>
+      <c r="B53"/>
+      <c r="C53"/>
+      <c r="E53"/>
+    </row>
+    <row r="54" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54"/>
+      <c r="B54"/>
+      <c r="C54"/>
+      <c r="E54"/>
+    </row>
+    <row r="55" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55"/>
+      <c r="B55"/>
+      <c r="C55"/>
+      <c r="E55"/>
+    </row>
+    <row r="56" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56"/>
+      <c r="B56"/>
+      <c r="C56"/>
+      <c r="E56"/>
+    </row>
+    <row r="57" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57"/>
+      <c r="B57"/>
+      <c r="C57"/>
+      <c r="E57"/>
+    </row>
+    <row r="58" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58"/>
+      <c r="B58"/>
+      <c r="C58"/>
+      <c r="E58"/>
+    </row>
+    <row r="59" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59"/>
+      <c r="B59"/>
+      <c r="C59"/>
+      <c r="E59"/>
+    </row>
+    <row r="60" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60"/>
+      <c r="B60"/>
+      <c r="C60"/>
+      <c r="E60"/>
+    </row>
   </sheetData>
-  <sortState ref="A2:E26">
-    <sortCondition ref="A2"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/excel-example/Old/Перевод позиций FOR MAPPING .xlsx
+++ b/excel-example/Old/Перевод позиций FOR MAPPING .xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="78">
   <si>
     <t>English</t>
   </si>
@@ -172,9 +172,6 @@
     <t xml:space="preserve">screws сountersunk structural self-tapping </t>
   </si>
   <si>
-    <t>screws GKD</t>
-  </si>
-  <si>
     <t>screws GKM</t>
   </si>
   <si>
@@ -242,6 +239,15 @@
   </si>
   <si>
     <t>screws UNIVERSAL yellow part thread</t>
+  </si>
+  <si>
+    <t>screws GKD 3_5</t>
+  </si>
+  <si>
+    <t>screws GKD 3_9</t>
+  </si>
+  <si>
+    <t>screws GKD 4_2</t>
   </si>
 </sst>
 </file>
@@ -642,7 +648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr defaultRowHeight="40.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="69.85546875" style="1" customWidth="1"/>
@@ -667,7 +673,7 @@
         <v>49</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>24</v>
@@ -681,7 +687,7 @@
         <v>50</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>39</v>
@@ -692,10 +698,10 @@
     </row>
     <row r="4" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>22</v>
@@ -706,13 +712,13 @@
     </row>
     <row r="5" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>33</v>
@@ -720,10 +726,10 @@
     </row>
     <row r="6" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>20</v>
@@ -734,10 +740,10 @@
     </row>
     <row r="7" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>21</v>
@@ -751,7 +757,7 @@
         <v>48</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>4</v>
@@ -762,10 +768,10 @@
     </row>
     <row r="9" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>46</v>
@@ -777,10 +783,10 @@
     </row>
     <row r="10" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>15</v>
@@ -791,10 +797,10 @@
     </row>
     <row r="11" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>42</v>
@@ -805,10 +811,10 @@
     </row>
     <row r="12" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>41</v>
@@ -819,10 +825,10 @@
     </row>
     <row r="13" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>44</v>
@@ -833,10 +839,10 @@
     </row>
     <row r="14" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>45</v>
@@ -847,52 +853,52 @@
     </row>
     <row r="15" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>7</v>
@@ -903,10 +909,10 @@
     </row>
     <row r="19" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>23</v>
@@ -917,10 +923,10 @@
     </row>
     <row r="20" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>13</v>
@@ -931,10 +937,10 @@
     </row>
     <row r="21" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>25</v>
@@ -945,10 +951,10 @@
     </row>
     <row r="22" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>19</v>
@@ -959,10 +965,10 @@
     </row>
     <row r="23" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>5</v>
@@ -973,10 +979,10 @@
     </row>
     <row r="24" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>17</v>
@@ -987,10 +993,10 @@
     </row>
     <row r="25" spans="1:5" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>40</v>
@@ -1004,7 +1010,7 @@
         <v>51</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>3</v>
@@ -1013,6 +1019,24 @@
       <c r="E26" s="6" t="s">
         <v>2</v>
       </c>
+    </row>
+    <row r="30" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30"/>
+      <c r="B30"/>
+      <c r="C30"/>
+      <c r="E30"/>
+    </row>
+    <row r="31" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31"/>
+      <c r="B31"/>
+      <c r="C31"/>
+      <c r="E31"/>
+    </row>
+    <row r="32" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32"/>
+      <c r="B32"/>
+      <c r="C32"/>
+      <c r="E32"/>
     </row>
     <row r="33" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33"/>
@@ -1182,6 +1206,12 @@
       <c r="C60"/>
       <c r="E60"/>
     </row>
+    <row r="61" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61"/>
+      <c r="B61"/>
+      <c r="C61"/>
+      <c r="E61"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
